--- a/Crown Institute of Higher Education/cihe.xlsx
+++ b/Crown Institute of Higher Education/cihe.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,16 @@
           <t>fee</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>enrolment_fee</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>materials_fee</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +477,12 @@
       <c r="E2" t="n">
         <v>54000</v>
       </c>
+      <c r="F2" t="n">
+        <v>250</v>
+      </c>
+      <c r="G2" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -492,6 +508,12 @@
       <c r="E3" t="n">
         <v>54000</v>
       </c>
+      <c r="F3" t="n">
+        <v>250</v>
+      </c>
+      <c r="G3" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -517,6 +539,12 @@
       <c r="E4" t="n">
         <v>54000</v>
       </c>
+      <c r="F4" t="n">
+        <v>250</v>
+      </c>
+      <c r="G4" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -542,6 +570,12 @@
       <c r="E5" t="n">
         <v>60000</v>
       </c>
+      <c r="F5" t="n">
+        <v>250</v>
+      </c>
+      <c r="G5" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -567,6 +601,12 @@
       <c r="E6" t="n">
         <v>80000</v>
       </c>
+      <c r="F6" t="n">
+        <v>250</v>
+      </c>
+      <c r="G6" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -592,6 +632,12 @@
       <c r="E7" t="n">
         <v>54000</v>
       </c>
+      <c r="F7" t="n">
+        <v>250</v>
+      </c>
+      <c r="G7" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -617,6 +663,12 @@
       <c r="E8" t="n">
         <v>18000</v>
       </c>
+      <c r="F8" t="n">
+        <v>250</v>
+      </c>
+      <c r="G8" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -642,6 +694,12 @@
       <c r="E9" t="n">
         <v>18000</v>
       </c>
+      <c r="F9" t="n">
+        <v>250</v>
+      </c>
+      <c r="G9" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -667,6 +725,12 @@
       <c r="E10" t="n">
         <v>18000</v>
       </c>
+      <c r="F10" t="n">
+        <v>250</v>
+      </c>
+      <c r="G10" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,14 +748,16 @@
           <t>https://www.cihe.edu.au/courses/eap/</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>0</v>
       </c>
+      <c r="F11" t="n">
+        <v>250</v>
+      </c>
+      <c r="G11" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -709,14 +775,16 @@
           <t>https://www.cihe.edu.au/courses/general-english/</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>0</v>
       </c>
+      <c r="F12" t="n">
+        <v>250</v>
+      </c>
+      <c r="G12" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -742,6 +810,12 @@
       <c r="E13" t="n">
         <v>9000</v>
       </c>
+      <c r="F13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G13" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -767,6 +841,12 @@
       <c r="E14" t="n">
         <v>17000</v>
       </c>
+      <c r="F14" t="n">
+        <v>250</v>
+      </c>
+      <c r="G14" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -792,6 +872,12 @@
       <c r="E15" t="n">
         <v>25000</v>
       </c>
+      <c r="F15" t="n">
+        <v>250</v>
+      </c>
+      <c r="G15" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -817,6 +903,12 @@
       <c r="E16" t="n">
         <v>44000</v>
       </c>
+      <c r="F16" t="n">
+        <v>250</v>
+      </c>
+      <c r="G16" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -842,6 +934,12 @@
       <c r="E17" t="n">
         <v>48000</v>
       </c>
+      <c r="F17" t="n">
+        <v>250</v>
+      </c>
+      <c r="G17" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -867,6 +965,12 @@
       <c r="E18" t="n">
         <v>33000</v>
       </c>
+      <c r="F18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G18" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -892,6 +996,12 @@
       <c r="E19" t="n">
         <v>68000</v>
       </c>
+      <c r="F19" t="n">
+        <v>250</v>
+      </c>
+      <c r="G19" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -917,6 +1027,12 @@
       <c r="E20" t="n">
         <v>50000</v>
       </c>
+      <c r="F20" t="n">
+        <v>250</v>
+      </c>
+      <c r="G20" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -942,6 +1058,12 @@
       <c r="E21" t="n">
         <v>33000</v>
       </c>
+      <c r="F21" t="n">
+        <v>250</v>
+      </c>
+      <c r="G21" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -966,6 +1088,12 @@
       </c>
       <c r="E22" t="n">
         <v>44000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>250</v>
+      </c>
+      <c r="G22" t="n">
+        <v>400</v>
       </c>
     </row>
   </sheetData>
